--- a/SGC-CKN/Excel/59879ec4-58d7-4242-8270-77eb6aaded98_Thanh_Hoá_P1-125_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/59879ec4-58d7-4242-8270-77eb6aaded98_Thanh_Hoá_P1-125_D800_29-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -178,6 +178,9 @@
   <si>
     <t xml:space="preserve">06:58
 29/03/2026</t>
+  </si>
+  <si>
+    <t>NT chạm sỏi CĐ: -35,33</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1146,19 +1149,19 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.86</v>
+        <v>-1.5</v>
       </c>
       <c r="H11" s="5">
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="J11" s="8">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1181,19 +1184,19 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.86</v>
+        <v>-1.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-5.41</v>
+        <v>-4.7</v>
       </c>
       <c r="H12" s="9">
         <v>0.83</v>
       </c>
       <c r="I12" s="9">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="J12" s="8">
-        <v>4.26</v>
+        <v>3.84</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1216,10 +1219,10 @@
         <v>36</v>
       </c>
       <c r="F13" s="12">
-        <v>-5.41</v>
+        <v>-4.7</v>
       </c>
       <c r="G13" s="12">
-        <v>-8.61</v>
+        <v>-7.9</v>
       </c>
       <c r="H13" s="12">
         <v>0.33</v>
@@ -1251,10 +1254,10 @@
         <v>39</v>
       </c>
       <c r="F14" s="16">
-        <v>-8.61</v>
+        <v>-7.9</v>
       </c>
       <c r="G14" s="16">
-        <v>-17.21</v>
+        <v>-16.5</v>
       </c>
       <c r="H14" s="16">
         <v>0.83</v>
@@ -1286,10 +1289,10 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-17.21</v>
+        <v>-16.5</v>
       </c>
       <c r="G15" s="19">
-        <v>-22.41</v>
+        <v>-21.7</v>
       </c>
       <c r="H15" s="19">
         <v>0.83</v>
@@ -1321,10 +1324,10 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
-        <v>-22.41</v>
+        <v>-21.7</v>
       </c>
       <c r="G16" s="22">
-        <v>-26.11</v>
+        <v>-25.4</v>
       </c>
       <c r="H16" s="22">
         <v>0.67</v>
@@ -1356,10 +1359,10 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-26.11</v>
+        <v>-25.4</v>
       </c>
       <c r="G17" s="25">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="H17" s="25">
         <v>0.97</v>
@@ -1391,10 +1394,10 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="G18" s="28">
-        <v>-45.08</v>
+        <v>-44.37</v>
       </c>
       <c r="H18" s="28">
         <v>3.5</v>
@@ -1406,12 +1409,12 @@
         <v>1.48</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1517,31 +1520,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1558,19 +1561,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.86</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="5">
         <v>0.33</v>
       </c>
       <c r="H2" s="5">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="8">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1587,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.86</v>
+        <v>-1.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-5.41</v>
+        <v>-4.7</v>
       </c>
       <c r="G3" s="9">
         <v>0.83</v>
       </c>
       <c r="H3" s="9">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="I3" s="8">
-        <v>4.26</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1616,10 +1619,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-5.41</v>
+        <v>-4.7</v>
       </c>
       <c r="F4" s="12">
-        <v>-8.61</v>
+        <v>-7.9</v>
       </c>
       <c r="G4" s="12">
         <v>0.33</v>
@@ -1645,10 +1648,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-8.61</v>
+        <v>-7.9</v>
       </c>
       <c r="F5" s="16">
-        <v>-17.21</v>
+        <v>-16.5</v>
       </c>
       <c r="G5" s="16">
         <v>0.83</v>
@@ -1674,10 +1677,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-17.21</v>
+        <v>-16.5</v>
       </c>
       <c r="F6" s="19">
-        <v>-22.41</v>
+        <v>-21.7</v>
       </c>
       <c r="G6" s="19">
         <v>0.83</v>
@@ -1703,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-22.41</v>
+        <v>-21.7</v>
       </c>
       <c r="F7" s="22">
-        <v>-26.11</v>
+        <v>-25.4</v>
       </c>
       <c r="G7" s="22">
         <v>0.67</v>
@@ -1732,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-26.11</v>
+        <v>-25.4</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="G8" s="25">
         <v>0.97</v>
@@ -1761,10 +1764,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="F9" s="28">
-        <v>-45.08</v>
+        <v>-44.37</v>
       </c>
       <c r="G9" s="28">
         <v>3.5</v>
@@ -1778,7 +1781,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>29</v>
@@ -1790,10 +1793,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-45.08</v>
+        <v>-44.37</v>
       </c>
       <c r="G10" s="33">
         <v>8.3</v>
